--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,20 +16,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,22 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,58 +413,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>지역</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>시군구</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>공고명</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>주택 유형</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>접수 시작일</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>접수 마감일</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>주택유형</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>공고일</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>마감일</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>원문 링크</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>남은 일수</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>공고 상태</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>대상 분류</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>마감 표시</t>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>D-Day</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>상태</t>
         </is>
       </c>
     </row>
@@ -492,41 +471,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>파주시</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>파주시 행복주택 예비입주자 모집공고(26.08.07)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>행복주택</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>46253</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020512&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+      <c r="H2" t="n">
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -538,41 +516,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>평택시</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>평택시 지역 행복주택 입주자격완화[선계약후검증] 예비입주자 모집(2026.08.05)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>행복주택</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>46253</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020492&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+      <c r="H3" t="n">
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -582,43 +559,38 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>행복주택</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>46254</v>
+          <t>[청년신혼부부매입임대리츠]_경기남부지역 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020519&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020480&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -630,41 +602,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_경기남부지역 예비입주자 모집</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>[청년신혼부부매입임대리츠]_경기북부지역 입주자 모집</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>매입임대</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>46254</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020480&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020487&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -676,41 +647,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>김포시 행복주택 입주자격완화 예비입주자 모집(26.08.06.)</t>
+          <t>구리시</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>행복주택</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>46254</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020525&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020536&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -722,41 +692,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
+          <t>구리시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>행복주택</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>46254</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020521&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020519&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -768,41 +737,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_경기북부지역 입주자 모집</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>매입임대</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>46254</v>
+          <t>김포시 행복주택 입주자격완화 예비입주자 모집(26.08.06.)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020487&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020525&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -814,41 +782,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>행복주택</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>46254</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020536&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020537&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -860,41 +827,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>남양주시</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>행복주택</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>46254</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020537&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020521&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -906,41 +872,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>행복주택</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>46259</v>
+          <t>장애인 자립특화형 주택 여기가 입주자 모집공고(경기도 김포시)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>9</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260821</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020539&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>D-9</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -952,41 +917,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
+          <t>화성시 동탄구</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>행복주택</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>46260</v>
+          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>D-10</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -998,41 +962,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
+          <t>의왕시</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>매입임대</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>46262</v>
+          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>12</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>D-12</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -1044,41 +1007,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
+          <t>성남시 수정구</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>행복주택</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>46261</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>46262</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>12</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>9</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>D-12</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -1090,41 +1052,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
+          <t>이천시</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>행복주택</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>46262</v>
+          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>통합공공임대</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>12</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20260827</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -1136,133 +1097,130 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>수원시 팔달구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>46387</v>
+          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>137</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>접수 중</t>
-        </is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>11</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>D-137</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>46077</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>46387</v>
+          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>137</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>접수 중</t>
-        </is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>11</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>D-137</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>46387</v>
+          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>20260827</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>137</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>접수 중</t>
-        </is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>11</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>청년 관련</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>D-137</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -1272,43 +1230,38 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>장애인 자립특화형 주택 여기가 입주자 모집공고(경기도 김포시)</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>매입임대</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>46255</v>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020539&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>마감 임박</t>
-        </is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>136</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>일반 공고</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>D-5</t>
+          <t>D-136</t>
         </is>
       </c>
     </row>
@@ -1318,43 +1271,38 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>영구임대</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>46258</v>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>136</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>일반 공고</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>D-8</t>
+          <t>D-136</t>
         </is>
       </c>
     </row>
@@ -1364,43 +1312,38 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>46259</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>46261</v>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>11</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>접수 예정</t>
-        </is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>136</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>일반 공고</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>D-11</t>
+          <t>D-136</t>
         </is>
       </c>
     </row>
@@ -1410,43 +1353,202 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>136</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>D-136</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
         <is>
           <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>전세임대</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>46387</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>137</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>접수 중</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>일반 공고</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>D-137</t>
+      <c r="H23" t="n">
+        <v>136</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>D-136</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>136</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>D-136</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>136</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>D-136</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>136</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>D-136</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -586,11 +586,11 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -631,11 +631,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -721,11 +721,11 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -766,11 +766,11 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -811,11 +811,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -856,11 +856,11 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -901,11 +901,11 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -946,11 +946,11 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
@@ -991,11 +991,11 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -1081,11 +1081,11 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -1126,11 +1126,11 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -1171,11 +1171,11 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -1216,11 +1216,11 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -1230,38 +1230,42 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>부천시 원미구</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-136</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1278,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1294,15 +1298,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-136</t>
+          <t>D-135</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1319,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1335,15 +1339,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-136</t>
+          <t>D-135</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1360,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1366,7 +1370,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1376,28 +1380,28 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-136</t>
+          <t>D-135</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1407,7 +1411,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1417,15 +1421,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-136</t>
+          <t>D-135</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1442,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1458,15 +1462,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-136</t>
+          <t>D-135</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1483,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1499,15 +1503,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-136</t>
+          <t>D-135</t>
         </is>
       </c>
     </row>
@@ -1520,35 +1524,76 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>135</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>전세임대</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>20260224</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>20261231</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>136</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>D-136</t>
+      <c r="H27" t="n">
+        <v>135</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>D-135</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,18 +556,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>김해시</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_경기남부지역 예비입주자 모집</t>
+          <t>김해진영2 B5블록(센텀큐브) 10년 공공임대주택리츠 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -577,37 +581,37 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260819</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020480&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061151&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_경기북부지역 입주자 모집</t>
+          <t>[청년신혼부부매입임대리츠]_강원지역 입주자 모집</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -627,7 +631,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020487&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020494&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -645,19 +649,15 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>구리시</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
+          <t>[청년신혼부부매입임대리츠]_경기남부지역 예비입주자 모집</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020536&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020480&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -692,17 +692,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>구리시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
+          <t>[청년신혼부부매입임대리츠]_경기북부지역 입주자 모집</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020519&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020487&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -737,12 +737,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>구리시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>김포시 행복주택 입주자격완화 예비입주자 모집(26.08.06.)</t>
+          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020525&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020536&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -782,12 +782,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>구리시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
+          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020537&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020519&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
+          <t>김포시 행복주택 입주자격완화 예비입주자 모집(26.08.06.)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020521&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020525&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -872,40 +872,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>장애인 자립특화형 주택 여기가 입주자 모집공고(경기도 김포시)</t>
+          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020539&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020537&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -917,17 +917,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>화성시 동탄구</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
+          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -937,172 +937,168 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020521&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>의왕시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
+          <t>[경남지역본부]26년 2차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020444&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>성남시 수정구</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
+          <t>[청년신혼부부매입임대리츠]_경남지역 입주자 모집</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020493&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>이천시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
+          <t>[청년신혼부부매입임대리츠]_대구경북지역 입주자 모집</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020491&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>수원시 팔달구</t>
+          <t>구미시</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
+          <t>경북서부(구미) 비분양전환형 든든전세주택 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1112,87 +1108,87 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020499&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>수성구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
+          <t>[청년신혼부부매입임대리츠]_대구경북지역 입주자 모집</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020491&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
+          <t>대구연경1 및 대구도남1·2 행복주택 입주자격 완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1202,398 +1198,5668 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020476&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+          <t>[청년신혼부부매입임대리츠]_대전충남지역 입주자 모집</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020489&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>동래구</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠]_부산지역 입주자 모집</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020463&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>미추홀구</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠]_인천지역 입주자 모집</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020486&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>[전북지역본부] 2026년 2차 전주시 든든전세주택 입주자 모집 공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020503&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>[청년신혼부부매입임대리츠]_전북지역 입주자 모집</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020481&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>군산오룡 고령자복지주택(영구임대) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020467&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>아산시</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠]_대전충남지역 입주자 모집</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020489&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>충주시</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>[청년신혼부부 매입임대리츠] 충북지역 입주자 모집</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020485&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>김포시</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>장애인 자립특화형 주택 여기가 입주자 모집공고(경기도 김포시)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>20260821</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020539&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>통영시</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>20260821</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020510&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>통영시</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>20260821</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020454&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>달성군</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[대구시 달서구,달성군] 일반 매입임대 입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>20260821</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020514&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>김제하동 국민임대주택 모집공고</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>20260821</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020527&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>익산시</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>익산부송1단지 주거복지동 영구임대주택 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>20260821</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020473&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>익산시</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>20260821</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020520&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>정읍시</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>정읍수성1 영구임대주택 모집공고</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>20260821</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020335&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>화성시 동탄구</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>D-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>청주시 서원구</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020440&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>D-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>청주시 서원구</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020423&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>D-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>의왕시</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>7</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026년 전세임대주택 입주자모집(제2차)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;idx=882115&amp;amode=view&amp;cpage=1&amp;stype=title&amp;upunit=50</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>7</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>영종구</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>7</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>영종구</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020411&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>7</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>고창군</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>고창율계 고령자복지주택(영구임대) 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020535&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>성남시 수정구</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>경산시</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>8</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>동구</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>8</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>부산진구</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>26년 2차 부산 분양전환형 든든전세 입주자 모집 공고</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020540&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>8</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>기장군</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020548&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>8</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>기장군</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020464&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>8</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>이천시</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>통합공공임대</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>20260827</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>9</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>D-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>화천군</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>수원시 팔달구</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>남양주시</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>10</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>화성시 효행구</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>20260827</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>경산시</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>경산시 영구임대주택 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>20260825</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>10</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>북구</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>10년임대</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20260827</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>10</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>금정구</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>10</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>괴산군</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>20260826</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>20260828</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>고령군</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>20260407</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>13</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>고령군</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>20260407</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>13</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>고령군</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>20260407</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>13</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>영도구</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>20260824</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>13</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>원주시</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>원주시지역 행복주택 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>15</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>부천시 원미구</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>15</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>아산시</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>15</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>청주시 서원구</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>15</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>강릉시</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>20260903</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>16</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>고성군</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>20260903</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>16</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>진주시</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>20260903</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>16</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>밀양시</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>20260904</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>17</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>D-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>동구</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>20260902</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>20260904</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>17</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>D-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>춘천시</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>23</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>D-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>김해시</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>24</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>D-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>58</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>D-58</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>양산시</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>72</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>D-72</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>20260511</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>20261030</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>73</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>D-73</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>[청년신혼부부매입임대리츠]경남지역 예비입주자 상시모집</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>20261130</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019919&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>104</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>20261130</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>104</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>20261130</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>104</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>행복주택</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>20261222</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>126</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>D-126</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>20260624</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>20261230</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>134</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>D-134</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>135</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>135</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>135</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>135</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>20260212</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>135</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>20260212</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>135</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>20260212</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>135</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>135</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>135</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>135</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>135</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>135</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>135</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>135</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>135</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>135</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>135</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>135</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>135</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>135</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>135</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>135</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>135</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>135</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>135</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>135</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>135</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>135</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>135</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>135</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>135</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>135</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>135</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>135</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
         <is>
           <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>전세임대</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>20260224</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>20261231</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="H115" t="n">
         <v>135</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>135</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>135</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>135</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>135</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>135</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>135</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>135</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>135</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>135</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>135</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>135</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>135</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>135</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>135</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>135</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>135</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>135</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>영구임대</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>135</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>135</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>135</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>135</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>135</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>135</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>135</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>135</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>135</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>20260316</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>135</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>135</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>135</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>135</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>135</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>D-135</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>347</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>D-347</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>1140</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>D-1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>1140</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>D-1140</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I149"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>파주시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>파주시 행복주택 예비입주자 모집공고(26.08.07)</t>
+          <t>[청년신혼부부매입임대리츠]_강원지역 입주자 모집</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,20 +491,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020512&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020494&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -514,19 +514,15 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>평택시</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>평택시 지역 행복주택 입주자격완화[선계약후검증] 예비입주자 모집(2026.08.05)</t>
+          <t>[청년신혼부부매입임대리츠]_경기남부지역 예비입주자 모집</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -536,42 +532,42 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020492&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020480&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>김해진영2 B5블록(센텀큐브) 10년 공공임대주택리츠 예비입주자 모집 공고</t>
+          <t>[청년신혼부부매입임대리츠]_경기북부지역 입주자 모집</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -581,42 +577,42 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061151&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020487&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>구리시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_강원지역 입주자 모집</t>
+          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -631,15 +627,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020494&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020536&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -649,15 +645,19 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>구리시</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_경기남부지역 예비입주자 모집</t>
+          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -672,15 +672,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020480&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020519&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_경기북부지역 입주자 모집</t>
+          <t>김포시 행복주택 입주자격완화 예비입주자 모집(26.08.06.)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -717,15 +717,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020487&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020525&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>구리시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
+          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -762,15 +762,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020536&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020537&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>구리시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
+          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -807,37 +807,37 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020519&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020521&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>김포시 행복주택 입주자격완화 예비입주자 모집(26.08.06.)</t>
+          <t>[경남지역본부]26년 2차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -852,37 +852,37 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020525&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020444&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
+          <t>[청년신혼부부매입임대리츠]_경남지역 입주자 모집</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -897,37 +897,37 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020537&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020493&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
+          <t>[청년신혼부부매입임대리츠]_대구경북지역 입주자 모집</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -942,32 +942,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020521&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020491&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>구미시</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 2차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
+          <t>경북서부(구미) 비분양전환형 든든전세주택 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -987,28 +987,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020444&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020499&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>수성구</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_경남지역 입주자 모집</t>
+          <t>[청년신혼부부매입임대리츠]_대구경북지역 입주자 모집</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1028,37 +1032,37 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020493&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020491&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_대구경북지역 입주자 모집</t>
+          <t>대구연경1 및 대구도남1·2 행복주택 입주자격 완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1073,32 +1077,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020491&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020476&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>구미시</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>경북서부(구미) 비분양전환형 든든전세주택 입주자 모집 공고</t>
+          <t>[청년신혼부부매입임대리츠]_대전충남지역 입주자 모집</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1118,32 +1122,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020499&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020489&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>수성구</t>
+          <t>동래구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_대구경북지역 입주자 모집</t>
+          <t>[청년신혼부부매입임대리츠]_부산지역 입주자 모집</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1163,37 +1167,37 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020491&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020463&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>미추홀구</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>대구연경1 및 대구도남1·2 행복주택 입주자격 완화 예비입주자 모집</t>
+          <t>[청년신혼부부매입임대리츠]_인천지역 입주자 모집</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1208,32 +1212,28 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020476&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020486&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대전</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>유성구</t>
-        </is>
-      </c>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_대전충남지역 입주자 모집</t>
+          <t>[전북지역본부] 2026년 2차 전주시 든든전세주택 입주자 모집 공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020489&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020503&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>동래구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_부산지역 입주자 모집</t>
+          <t>[청년신혼부부매입임대리츠]_전북지역 입주자 모집</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1298,37 +1298,37 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020463&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020481&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_인천지역 입주자 모집</t>
+          <t>군산오룡 고령자복지주택(영구임대) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1343,28 +1343,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020486&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020467&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>아산시</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[전북지역본부] 2026년 2차 전주시 든든전세주택 입주자 모집 공고(비분양전환형)</t>
+          <t>[청년신혼부부매입임대리츠]_대전충남지역 입주자 모집</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1384,32 +1388,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020503&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020489&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>충주시</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_전북지역 입주자 모집</t>
+          <t>[청년신혼부부 매입임대리츠] 충북지역 입주자 모집</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1429,82 +1433,82 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020481&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020485&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>군산오룡 고령자복지주택(영구임대) 예비입주자 추가모집</t>
+          <t>장애인 자립특화형 주택 여기가 입주자 모집공고(경기도 김포시)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020467&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020539&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_대전충남지역 입주자 모집</t>
+          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1514,42 +1518,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020489&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020510&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>충주시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[청년신혼부부 매입임대리츠] 충북지역 입주자 모집</t>
+          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1559,37 +1563,37 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020485&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020454&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>달성군</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>장애인 자립특화형 주택 여기가 입주자 모집공고(경기도 김포시)</t>
+          <t>[대구시 달서구,달성군] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1599,7 +1603,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260819</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1609,42 +1613,42 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020539&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020514&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
+          <t>김제하동 국민임대주택 모집공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260819</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1654,32 +1658,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020510&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020527&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
+          <t>익산부송1단지 주거복지동 영구임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1699,42 +1703,42 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020454&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020473&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>달성군</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[대구시 달서구,달성군] 일반 매입임대 입주자 모집공고</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1744,15 +1748,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020514&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020520&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1764,22 +1768,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>김제하동 국민임대주택 모집공고</t>
+          <t>정읍수성1 영구임대주택 모집공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1789,32 +1793,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020527&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020335&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>화성시 동탄구</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>익산부송1단지 주거복지동 영구임대주택 예비입주자 모집공고</t>
+          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1829,82 +1833,82 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020473&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020520&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020440&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>정읍수성1 영구임대주택 모집공고</t>
+          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1914,25 +1918,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020335&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020423&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -1944,147 +1948,143 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>화성시 동탄구</t>
+          <t>의왕시</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
+          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>청주시 서원구</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
+          <t>2026년 전세임대주택 입주자모집(제2차)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260819</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020440&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;idx=882115&amp;amode=view&amp;cpage=1&amp;stype=title&amp;upunit=50</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>영종구</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
+          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020423&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>의왕시</t>
+          <t>영종구</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
+          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2104,38 +2104,42 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020411&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>고창군</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 전세임대주택 입주자모집(제2차)</t>
+          <t>고창율계 고령자복지주택(영구임대) 예비입주자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2145,32 +2149,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;idx=882115&amp;amode=view&amp;cpage=1&amp;stype=title&amp;upunit=50</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020535&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>성남시 수정구</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2185,42 +2189,42 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2230,42 +2234,42 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020411&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>고창군</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>고창율계 고령자복지주택(영구임대) 예비입주자 모집</t>
+          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2275,42 +2279,42 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020535&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>성남시 수정구</t>
+          <t>부산진구</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
+          <t>26년 2차 부산 분양전환형 든든전세 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2325,42 +2329,42 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020540&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2370,42 +2374,42 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020548&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2415,97 +2419,97 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020464&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>부산진구</t>
+          <t>이천시</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>26년 2차 부산 분양전환형 든든전세 입주자 모집 공고</t>
+          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020540&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>화천군</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020548&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -2520,37 +2524,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>수원시 권선구</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020464&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -2570,17 +2574,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>이천시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
+          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2590,47 +2594,47 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>화천군</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
+          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2640,42 +2644,42 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>수원시 팔달구</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
+          <t>경산시 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2685,42 +2689,42 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
+          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2730,42 +2734,42 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>금정구</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
+          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2775,42 +2779,42 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>괴산군</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>경산시 영구임대주택 예비입주자 모집</t>
+          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2820,77 +2824,77 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>금정구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
+          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2900,97 +2904,97 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>괴산군</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
+          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>영도구</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
+          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3000,142 +3004,142 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
+          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
+          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>영도구</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
+          <t>원주시지역 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -3150,17 +3154,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>원주시지역 행복주택 예비입주자 모집</t>
+          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3170,7 +3174,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3180,32 +3184,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3225,15 +3229,15 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
@@ -3274,11 +3278,11 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
@@ -3319,11 +3323,11 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
@@ -3364,11 +3368,11 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -3409,11 +3413,11 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -3454,73 +3458,73 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>의성군</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3535,42 +3539,42 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3580,20 +3584,20 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-23</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
@@ -3605,57 +3609,57 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-24</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>김천시</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3665,70 +3669,70 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-58</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-72</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
@@ -3740,515 +3744,531 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-73</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>완주군</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]경남지역 예비입주자 상시모집</t>
+          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019919&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-18</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-104</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-126</t>
+          <t>D-22</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-134</t>
+          <t>D-56</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>양산시</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-70</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-71</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠]경남지역 예비입주자 상시모집</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019919&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-102</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-124</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4280,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4275,32 +4295,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4330,18 +4350,18 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4371,18 +4391,18 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -4412,18 +4432,18 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -4453,34 +4473,38 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4490,38 +4514,42 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4531,38 +4559,42 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4572,28 +4604,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4603,7 +4635,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4613,28 +4645,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4654,28 +4686,28 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4695,28 +4727,28 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4726,7 +4758,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4736,28 +4768,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4767,7 +4799,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4777,28 +4809,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4818,28 +4850,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4859,28 +4891,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4890,7 +4922,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4900,28 +4932,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4931,7 +4963,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4941,28 +4973,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4982,28 +5014,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5023,28 +5055,28 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5054,7 +5086,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5064,28 +5096,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5095,7 +5127,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5105,28 +5137,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5146,28 +5178,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5187,28 +5219,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5218,7 +5250,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5228,28 +5260,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5259,7 +5291,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5269,28 +5301,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5310,28 +5342,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5351,28 +5383,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5382,7 +5414,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5392,28 +5424,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5423,7 +5455,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5433,28 +5465,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5474,28 +5506,28 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5515,28 +5547,28 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5546,7 +5578,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5556,28 +5588,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5587,7 +5619,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5597,28 +5629,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5638,28 +5670,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5679,28 +5711,28 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5710,7 +5742,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5720,28 +5752,28 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5751,7 +5783,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5761,28 +5793,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5802,28 +5834,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5843,28 +5875,28 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5874,7 +5906,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5884,28 +5916,28 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5915,7 +5947,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5925,28 +5957,28 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5966,28 +5998,28 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6007,28 +6039,28 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6038,7 +6070,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6048,28 +6080,28 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6079,7 +6111,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6089,42 +6121,38 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6134,42 +6162,38 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6179,28 +6203,28 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6210,7 +6234,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6220,28 +6244,28 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6261,28 +6285,28 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6302,28 +6326,28 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6333,7 +6357,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6343,28 +6367,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6374,7 +6398,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6384,38 +6408,42 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6425,38 +6453,42 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6466,28 +6498,28 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6497,7 +6529,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6507,42 +6539,38 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6552,28 +6580,28 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6593,28 +6621,28 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6624,7 +6652,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6634,28 +6662,28 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6675,28 +6703,28 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6706,7 +6734,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6716,150 +6744,441 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>D-135</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>347</v>
+        <v>133</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>D-347</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>20250929</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>20291001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1140</v>
+        <v>133</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>D-1140</t>
+          <t>D-133</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>20260316</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>133</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>D-133</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>133</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>D-133</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>133</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>D-133</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>133</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>D-133</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>133</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>D-133</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>345</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>D-345</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>울주군</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>국민임대</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>20250929</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>20291001</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>1138</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>D-1138</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H149" t="n">
-        <v>1140</v>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>D-1140</t>
+      <c r="H156" t="n">
+        <v>1138</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>D-1138</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_강원지역 입주자 모집</t>
+          <t>장애인 자립특화형 주택 여기가 입주자 모집공고(경기도 김포시)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020494&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020539&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -511,18 +511,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>통영시</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_경기남부지역 예비입주자 모집</t>
+          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -532,12 +536,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020480&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020510&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -552,22 +556,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_경기북부지역 입주자 모집</t>
+          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -577,12 +581,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020487&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020454&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -597,37 +601,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>구리시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
+          <t>[대구시 달서구,달성군] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260819</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020536&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020514&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -642,37 +646,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>구리시</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>구리,남양주시 행복주택 예비입주자모집(26.08.05공고)</t>
+          <t>김제하동 국민임대주택 모집공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260819</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020519&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020527&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -687,22 +691,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>김포시 행복주택 입주자격완화 예비입주자 모집(26.08.06.)</t>
+          <t>익산부송1단지 주거복지동 영구임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -712,12 +716,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020525&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020473&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -732,37 +736,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
+          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020537&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020520&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -777,37 +781,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>남양주 장현5 2BL 행복주택 예비입주자 입주자격완화 모집(2026.08.05.공고)</t>
+          <t>정읍수성1 영구임대주택 모집공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260821</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020521&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020335&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -822,22 +826,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>화성시 동탄구</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[경남지역본부]26년 2차 분양전환형 든든전세주택 예비입주자 모집 공고</t>
+          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -847,42 +851,42 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020444&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_경남지역 입주자 모집</t>
+          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -892,42 +896,42 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020493&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020440&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_대구경북지역 입주자 모집</t>
+          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -937,127 +941,123 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020491&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020423&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>구미시</t>
+          <t>의왕시</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>경북서부(구미) 비분양전환형 든든전세주택 입주자 모집 공고</t>
+          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020499&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대구</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>수성구</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_대구경북지역 입주자 모집</t>
+          <t>2026년 전세임대주택 입주자모집(제2차)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260819</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020491&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;idx=882115&amp;amode=view&amp;cpage=1&amp;stype=title&amp;upunit=50</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>영종구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>대구연경1 및 대구도남1·2 행복주택 입주자격 완화 예비입주자 모집</t>
+          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1067,173 +1067,177 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020476&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>유성구</t>
+          <t>영종구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_대전충남지역 입주자 모집</t>
+          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020489&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020411&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>동래구</t>
+          <t>고창군</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_부산지역 입주자 모집</t>
+          <t>고창율계 고령자복지주택(영구임대) 예비입주자 모집</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020463&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020535&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>성남시 수정구</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_인천지역 입주자 모집</t>
+          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020486&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>경산시</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[전북지역본부] 2026년 2차 전주시 든든전세주택 입주자 모집 공고(비분양전환형)</t>
+          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1243,42 +1247,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020503&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_전북지역 입주자 모집</t>
+          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1288,160 +1292,160 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020481&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>사상구</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>군산오룡 고령자복지주택(영구임대) 예비입주자 추가모집</t>
+          <t>26년 2차 부산 분양전환형 든든전세 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020467&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020540&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]_대전충남지역 입주자 모집</t>
+          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020489&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020548&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>충주시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[청년신혼부부 매입임대리츠] 충북지역 입주자 모집</t>
+          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020485&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020464&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1453,57 +1457,57 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>이천시</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>장애인 자립특화형 주택 여기가 입주자 모집공고(경기도 김포시)</t>
+          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020539&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>화천군</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
+          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1513,177 +1517,177 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020510&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>수원시 권선구</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
+          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020454&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>달성군</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[대구시 달서구,달성군] 일반 매입임대 입주자 모집공고</t>
+          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020514&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>김제하동 국민임대주택 모집공고</t>
+          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020527&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>익산부송1단지 주거복지동 영구임대주택 예비입주자 모집공고</t>
+          <t>경산시 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1693,353 +1697,357 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020473&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020520&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>금정구</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>정읍수성1 영구임대주택 모집공고</t>
+          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020335&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>화성시 동탄구</t>
+          <t>괴산군</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
+          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
+          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020440&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
+          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020423&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>의왕시</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
+          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>영도구</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 전세임대주택 입주자모집(제2차)</t>
+          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;idx=882115&amp;amode=view&amp;cpage=1&amp;stype=title&amp;upunit=50</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2049,42 +2057,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2094,70 +2102,70 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020411&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>고창군</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>고창율계 고령자복지주택(영구임대) 예비입주자 모집</t>
+          <t>원주시지역 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020535&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2169,12 +2177,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>성남시 수정구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
+          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2184,312 +2192,312 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>부산진구</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>26년 2차 부산 분양전환형 든든전세 입주자 모집 공고</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020540&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020548&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020464&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>이천시</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>화천군</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2499,132 +2507,132 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>수원시 권선구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
+          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2634,295 +2642,295 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>경산시 영구임대주택 예비입주자 모집</t>
+          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>금정구</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
+          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>괴산군</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
+          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
+          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
+          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
@@ -2934,107 +2942,107 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>의성군</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
+          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>영도구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
+          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3044,42 +3052,42 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3089,82 +3097,82 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>김천시</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>원주시지역 행복주택 예비입주자 모집</t>
+          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3174,42 +3182,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3219,42 +3227,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
+          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3264,47 +3272,47 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3314,20 +3322,20 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
@@ -3339,40 +3347,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
@@ -3384,130 +3392,130 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-55</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>의성군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-69</t>
         </is>
       </c>
     </row>
@@ -3519,102 +3527,98 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-70</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>평택시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
+          <t>[청년신혼부부매입임대리츠]경남지역 예비입주자 상시모집</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019919&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-101</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3624,25 +3628,25 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-101</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3658,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3669,42 +3673,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-101</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3714,160 +3718,152 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>완주군</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>서귀포시</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
@@ -3877,149 +3873,141 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>춘천시</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>김해시</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-56</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4029,283 +4017,267 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-70</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-71</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]경남지역 예비입주자 상시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019919&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-102</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-102</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-102</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>포항시 남구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-124</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -4320,13 +4292,13 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4346,28 +4318,28 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4387,28 +4359,28 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4418,7 +4390,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4428,28 +4400,28 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4459,7 +4431,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4469,42 +4441,38 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4514,42 +4482,38 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4559,42 +4523,38 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4604,22 +4564,22 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4649,18 +4609,18 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4690,18 +4650,18 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4731,18 +4691,18 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4772,18 +4732,18 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4813,18 +4773,18 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4854,18 +4814,18 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4895,18 +4855,18 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4936,18 +4896,18 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4977,18 +4937,18 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -5018,18 +4978,18 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -5059,18 +5019,18 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -5100,18 +5060,18 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -5141,18 +5101,18 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -5182,18 +5142,18 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -5223,18 +5183,18 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -5264,18 +5224,18 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -5305,18 +5265,18 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -5346,18 +5306,18 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -5387,18 +5347,18 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -5428,18 +5388,18 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -5469,18 +5429,18 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -5510,18 +5470,18 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -5551,18 +5511,18 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -5592,18 +5552,18 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -5633,18 +5593,18 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5674,18 +5634,18 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -5715,18 +5675,18 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5756,18 +5716,18 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5797,18 +5757,18 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5838,18 +5798,18 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5879,18 +5839,18 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5920,34 +5880,38 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5957,38 +5921,42 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5998,28 +5966,28 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6039,28 +6007,28 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6070,7 +6038,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6080,28 +6048,28 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6121,28 +6089,28 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6152,7 +6120,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6162,28 +6130,28 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6203,28 +6171,28 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6234,7 +6202,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6244,28 +6212,28 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6285,28 +6253,28 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6316,7 +6284,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6326,38 +6294,42 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6367,28 +6339,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6398,7 +6370,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6408,42 +6380,38 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6453,42 +6421,38 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6498,28 +6462,28 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6529,7 +6493,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6539,646 +6503,150 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-132</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260812</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270731</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>133</v>
+        <v>344</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-344</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>133</v>
+        <v>1137</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-133</t>
+          <t>D-1137</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>133</v>
+        <v>1137</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-133</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>133</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>D-133</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>133</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>D-133</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H147" t="n">
-        <v>133</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>D-133</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
-        <v>133</v>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>D-133</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>매입임대</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H149" t="n">
-        <v>133</v>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>D-133</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H150" t="n">
-        <v>133</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>D-133</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H151" t="n">
-        <v>133</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>D-133</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H152" t="n">
-        <v>133</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>D-133</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H153" t="n">
-        <v>133</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>D-133</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>20260812</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>20270731</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H154" t="n">
-        <v>345</v>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>D-345</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H155" t="n">
-        <v>1138</v>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>D-1138</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H156" t="n">
-        <v>1138</v>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>D-1138</t>
+          <t>D-1137</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I144"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,57 +471,57 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>화성시 동탄구</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>장애인 자립특화형 주택 여기가 입주자 모집공고(경기도 김포시)</t>
+          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020539&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
+          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -536,37 +536,37 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020510&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020440&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>경남 통영안정 영구임대 예비입주자 모집(‘26.07.30.)</t>
+          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -581,87 +581,83 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020454&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020423&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>의왕시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[대구시 달서구,달성군] 일반 매입임대 입주자 모집공고</t>
+          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020514&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>김제하동 국민임대주택 모집공고</t>
+          <t>2026년 전세임대주택 입주자모집(제2차)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -671,110 +667,110 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020527&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;idx=882115&amp;amode=view&amp;cpage=1&amp;stype=title&amp;upunit=50</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>영종구</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>익산부송1단지 주거복지동 영구임대주택 예비입주자 모집공고</t>
+          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020473&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>영종구</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>익산한스빌 국민임대주택 예비입주자 자격완화 모집 공고</t>
+          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020520&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020411&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -786,12 +782,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>고창군</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>정읍수성1 영구임대주택 모집공고</t>
+          <t>고창율계 고령자복지주택(영구임대) 예비입주자 모집</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -801,25 +797,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260821</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020335&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020535&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -831,152 +827,152 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>화성시 동탄구</t>
+          <t>성남시 수정구</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
+          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
+          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020440&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
+          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020423&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>의왕시</t>
+          <t>사상구</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
+          <t>26년 2차 부산 분양전환형 든든전세 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -986,12 +982,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020540&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1006,33 +1002,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>기장군</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 전세임대주택 입주자모집(제2차)</t>
+          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;idx=882115&amp;amode=view&amp;cpage=1&amp;stype=title&amp;upunit=50</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020548&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1047,17 +1047,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1067,17 +1067,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020464&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1092,62 +1092,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>이천시</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020411&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>고창군</t>
+          <t>화천군</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>고창율계 고령자복지주택(영구임대) 예비입주자 모집</t>
+          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1162,20 +1162,20 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020535&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>성남시 수정구</t>
+          <t>수원시 팔달구</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
+          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1207,200 +1207,200 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>사상구</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>26년 2차 부산 분양전환형 든든전세 입주자 모집 공고</t>
+          <t>경산시 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020540&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020548&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
@@ -1412,77 +1412,77 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>금정구</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020464&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>이천시</t>
+          <t>괴산군</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
+          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1497,62 +1497,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>화천군</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
+          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>수원시 권선구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
+          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1562,267 +1562,267 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
+          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>영도구</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
+          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>경산시 영구임대주택 예비입주자 모집</t>
+          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>금정구</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
+          <t>원주시지역 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>괴산군</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
+          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1832,177 +1832,177 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
+          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>영도구</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
+          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2012,47 +2012,47 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2082,22 +2082,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2127,27 +2127,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>원주시지역 행복주택 예비입주자 모집</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2157,37 +2157,37 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2202,32 +2202,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2247,37 +2247,37 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2292,37 +2292,37 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2337,37 +2337,37 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
+          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2382,37 +2382,37 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2427,42 +2427,42 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2472,52 +2472,52 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -2532,37 +2532,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -2577,22 +2577,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2622,17 +2622,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
+          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -2667,37 +2667,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>의성군</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
+          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -2712,22 +2712,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
+          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2757,37 +2757,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
+          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -2802,17 +2802,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2822,17 +2822,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -2847,22 +2847,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>김천시</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -2892,17 +2892,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2912,17 +2912,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -2937,17 +2937,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>의성군</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
+          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2957,17 +2957,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
+          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -3027,67 +3027,67 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>구로구</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
+          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260906</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://happydorm.or.kr/gaebong/ko/index</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3097,42 +3097,42 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3142,307 +3142,303 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-54</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-68</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-69</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>춘천시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>[청년신혼부부매입임대리츠]경남지역 예비입주자 상시모집</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019919&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-100</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-100</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3452,291 +3448,279 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-55</t>
+          <t>D-100</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-69</t>
+          <t>D-122</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-70</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]경남지역 예비입주자 상시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019919&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-101</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-101</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-101</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>포항시 남구</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
@@ -3748,12 +3732,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3763,17 +3747,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -3791,20 +3775,24 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3814,15 +3802,15 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
@@ -3832,20 +3820,24 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3855,28 +3847,28 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3896,28 +3888,28 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3927,7 +3919,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3937,42 +3929,38 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3982,42 +3970,38 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4027,42 +4011,38 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4072,28 +4052,28 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4113,28 +4093,28 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4154,28 +4134,28 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4185,7 +4165,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4195,28 +4175,28 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4226,7 +4206,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4236,28 +4216,28 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4277,28 +4257,28 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4318,28 +4298,28 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4349,7 +4329,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4359,28 +4339,28 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4390,7 +4370,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4400,28 +4380,28 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4441,28 +4421,28 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4482,28 +4462,28 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4513,7 +4493,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4523,28 +4503,28 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4554,7 +4534,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4564,28 +4544,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4605,28 +4585,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4646,28 +4626,28 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4677,7 +4657,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4687,28 +4667,28 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4718,7 +4698,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4728,28 +4708,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4769,28 +4749,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4810,28 +4790,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4841,7 +4821,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4851,28 +4831,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4882,7 +4862,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4892,28 +4872,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4933,28 +4913,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4974,28 +4954,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5005,7 +4985,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5015,28 +4995,28 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5046,7 +5026,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5056,28 +5036,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5097,28 +5077,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5138,28 +5118,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5169,7 +5149,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5179,28 +5159,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5210,7 +5190,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5220,28 +5200,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5261,28 +5241,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5302,28 +5282,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5333,7 +5313,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5343,28 +5323,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5374,7 +5354,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5384,28 +5364,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5425,28 +5405,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5466,28 +5446,28 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5497,7 +5477,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5507,28 +5487,28 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5538,7 +5518,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5548,28 +5528,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5589,28 +5569,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5630,28 +5610,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5661,7 +5641,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5671,38 +5651,42 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5712,15 +5696,15 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
@@ -5730,20 +5714,24 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5753,28 +5741,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5794,28 +5782,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5835,28 +5823,28 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5866,7 +5854,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5876,42 +5864,38 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5921,42 +5905,38 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5966,28 +5946,28 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6007,28 +5987,28 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6048,28 +6028,28 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6079,7 +6059,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6089,38 +6069,42 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6130,22 +6114,22 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -6175,18 +6159,18 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -6216,18 +6200,18 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -6257,18 +6241,18 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -6298,355 +6282,146 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-131</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260812</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270731</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>132</v>
+        <v>343</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-343</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>132</v>
+        <v>1136</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-132</t>
+          <t>D-1136</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>132</v>
+        <v>1136</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-132</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H140" t="n">
-        <v>132</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>D-132</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H141" t="n">
-        <v>132</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>D-132</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>20260812</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>20270731</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H142" t="n">
-        <v>344</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>D-344</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>1137</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>D-1137</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>1137</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>D-1137</t>
+          <t>D-1136</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -590,11 +590,11 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -721,11 +721,11 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -766,11 +766,11 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -811,11 +811,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
@@ -856,11 +856,11 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -901,11 +901,11 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -946,11 +946,11 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -991,11 +991,11 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1081,11 +1081,11 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1126,11 +1126,11 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
@@ -1171,11 +1171,11 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1216,11 +1216,11 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1261,11 +1261,11 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1306,11 +1306,11 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1351,11 +1351,11 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1396,11 +1396,11 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1441,11 +1441,11 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1531,11 +1531,11 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -1576,11 +1576,11 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -1621,11 +1621,11 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -1666,11 +1666,11 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -1711,11 +1711,11 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -1756,11 +1756,11 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
@@ -1801,11 +1801,11 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -1846,11 +1846,11 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -1891,11 +1891,11 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -1936,11 +1936,11 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -1981,11 +1981,11 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2026,11 +2026,11 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2071,11 +2071,11 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2116,11 +2116,11 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2161,11 +2161,11 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2206,11 +2206,11 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2251,11 +2251,11 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2296,11 +2296,11 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2341,11 +2341,11 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2386,11 +2386,11 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2431,11 +2431,11 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2476,11 +2476,11 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
@@ -2521,11 +2521,11 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -2566,11 +2566,11 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -2611,11 +2611,11 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -2656,11 +2656,11 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -2701,11 +2701,11 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -2746,11 +2746,11 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -2791,11 +2791,11 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2836,11 +2836,11 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2881,11 +2881,11 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2926,11 +2926,11 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -3016,11 +3016,11 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -3061,11 +3061,11 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -3106,11 +3106,11 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
@@ -3151,11 +3151,11 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-18</t>
         </is>
       </c>
     </row>
@@ -3196,11 +3196,11 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
@@ -3241,11 +3241,11 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-54</t>
+          <t>D-53</t>
         </is>
       </c>
     </row>
@@ -3286,11 +3286,11 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-68</t>
+          <t>D-67</t>
         </is>
       </c>
     </row>
@@ -3331,11 +3331,11 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-69</t>
+          <t>D-68</t>
         </is>
       </c>
     </row>
@@ -3372,11 +3372,11 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-100</t>
+          <t>D-99</t>
         </is>
       </c>
     </row>
@@ -3417,11 +3417,11 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-100</t>
+          <t>D-99</t>
         </is>
       </c>
     </row>
@@ -3462,11 +3462,11 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-100</t>
+          <t>D-99</t>
         </is>
       </c>
     </row>
@@ -3507,11 +3507,11 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-122</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -3552,11 +3552,11 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-129</t>
         </is>
       </c>
     </row>
@@ -3593,11 +3593,11 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -3634,11 +3634,11 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -3675,11 +3675,11 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -3716,11 +3716,11 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -3761,11 +3761,11 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -3806,11 +3806,11 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -3851,11 +3851,11 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -3892,11 +3892,11 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -3933,11 +3933,11 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -3974,11 +3974,11 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4056,11 +4056,11 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4097,11 +4097,11 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4138,11 +4138,11 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4179,11 +4179,11 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4220,11 +4220,11 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4261,11 +4261,11 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4302,11 +4302,11 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4343,11 +4343,11 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4384,11 +4384,11 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4425,11 +4425,11 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4466,11 +4466,11 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4507,11 +4507,11 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4548,11 +4548,11 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4589,11 +4589,11 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4630,11 +4630,11 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4671,11 +4671,11 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4712,11 +4712,11 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4753,11 +4753,11 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4794,11 +4794,11 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4835,11 +4835,11 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4876,11 +4876,11 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4917,11 +4917,11 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4958,11 +4958,11 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -4999,11 +4999,11 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5040,11 +5040,11 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5081,11 +5081,11 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5122,11 +5122,11 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5163,11 +5163,11 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5204,11 +5204,11 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5245,11 +5245,11 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5286,11 +5286,11 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5327,11 +5327,11 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5368,11 +5368,11 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5409,11 +5409,11 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5450,11 +5450,11 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5491,11 +5491,11 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5532,11 +5532,11 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5573,11 +5573,11 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5614,11 +5614,11 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5655,11 +5655,11 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5700,11 +5700,11 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5745,11 +5745,11 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5786,11 +5786,11 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5827,11 +5827,11 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5868,11 +5868,11 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5909,11 +5909,11 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5950,11 +5950,11 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -5991,11 +5991,11 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -6032,11 +6032,11 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -6073,11 +6073,11 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -6118,11 +6118,11 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -6159,11 +6159,11 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -6200,11 +6200,11 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -6241,11 +6241,11 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -6282,11 +6282,11 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-131</t>
+          <t>D-130</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-343</t>
+          <t>D-342</t>
         </is>
       </c>
     </row>
@@ -6372,11 +6372,11 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-1136</t>
+          <t>D-1135</t>
         </is>
       </c>
     </row>
@@ -6417,11 +6417,11 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-1136</t>
+          <t>D-1135</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,147 +471,143 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>화성시 동탄구</t>
+          <t>의왕시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>화성시 동탄지역 영구임대주택 예비입주자 모집(‘26.08.05.)</t>
+          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020515&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>청주시 서원구</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
+          <t>2026년 전세임대주택 입주자모집(제2차)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260819</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020440&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;idx=882115&amp;amode=view&amp;cpage=1&amp;stype=title&amp;upunit=50</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>영종구</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>청주산남2-2단지 영구임대 예비입주자 모집</t>
+          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260818</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020423&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>의왕시</t>
+          <t>영종구</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
+          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -631,38 +627,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020411&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>고창군</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 전세임대주택 입주자모집(제2차)</t>
+          <t>고창율계 고령자복지주택(영구임대) 예비입주자 모집</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -672,32 +672,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;idx=882115&amp;amode=view&amp;cpage=1&amp;stype=title&amp;upunit=50</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020535&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>성남시 수정구</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -712,42 +712,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -757,42 +757,42 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020411&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>고창군</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>고창율계 고령자복지주택(영구임대) 예비입주자 모집</t>
+          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -802,42 +802,42 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020535&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>성남시 수정구</t>
+          <t>사상구</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
+          <t>26년 2차 부산 분양전환형 든든전세 입주자 모집 공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -852,42 +852,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020540&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -897,42 +897,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020548&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -942,97 +942,97 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020464&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>사상구</t>
+          <t>이천시</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>26년 2차 부산 분양전환형 든든전세 입주자 모집 공고</t>
+          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020540&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>화천군</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020548&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1047,37 +1047,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>수원시 팔달구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020464&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>이천시</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
+          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>화천군</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
+          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1167,42 +1167,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>수원시 팔달구</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
+          <t>경산시 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1212,42 +1212,42 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
+          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1257,42 +1257,42 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>금정구</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
+          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1302,42 +1302,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>괴산군</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>경산시 영구임대주택 예비입주자 모집</t>
+          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1347,77 +1347,77 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>금정구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
+          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1427,97 +1427,97 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>괴산군</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
+          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>영도구</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
+          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1527,142 +1527,142 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
+          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
+          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>영도구</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
+          <t>원주시지역 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1677,17 +1677,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1702,42 +1702,42 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1747,37 +1747,37 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>원주시지역 행복주택 예비입주자 모집</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1797,32 +1797,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1842,32 +1842,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
+          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1887,37 +1887,37 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1932,37 +1932,37 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1977,15 +1977,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2022,15 +2022,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2067,15 +2067,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2112,15 +2112,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2157,15 +2157,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2202,37 +2202,37 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2247,37 +2247,37 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2292,42 +2292,42 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
+          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2372,42 +2372,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
+          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2417,87 +2417,87 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
+          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
+          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2517,37 +2517,37 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>의성군</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
+          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2562,32 +2562,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2607,37 +2607,37 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2647,137 +2647,137 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>의성군</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>김천시</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
+          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2787,42 +2787,42 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2832,42 +2832,42 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
+          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2877,32 +2877,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>구로구</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2912,17 +2912,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260906</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://happydorm.or.kr/gaebong/ko/index</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -2937,17 +2937,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2957,187 +2957,179 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>연제구</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
+          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>구로구</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20260906</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://happydorm.or.kr/gaebong/ko/index</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>서귀포시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>춘천시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3147,32 +3139,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3192,122 +3184,122 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-53</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-67</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3317,83 +3309,87 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-68</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>안동시</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]경남지역 예비입주자 상시모집</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019919&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-99</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3403,283 +3399,291 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-99</t>
+          <t>D-51</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-99</t>
+          <t>D-65</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-66</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>[청년신혼부부매입임대리츠]경남지역 예비입주자 상시모집</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019919&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-129</t>
+          <t>D-97</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-97</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-97</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
@@ -3689,38 +3693,42 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-127</t>
         </is>
       </c>
     </row>
@@ -3730,24 +3738,20 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3757,15 +3761,15 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
@@ -3775,24 +3779,20 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3802,15 +3802,15 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
@@ -3820,24 +3820,20 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3847,28 +3843,28 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3878,7 +3874,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3888,38 +3884,42 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3929,38 +3929,42 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3970,38 +3974,42 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4011,22 +4019,22 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -4056,18 +4064,18 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -4097,18 +4105,18 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -4138,18 +4146,18 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -4179,18 +4187,18 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -4220,18 +4228,18 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4261,18 +4269,18 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4302,18 +4310,18 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4343,18 +4351,18 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -4384,18 +4392,18 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -4425,18 +4433,18 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4466,18 +4474,18 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4507,18 +4515,18 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4548,18 +4556,18 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4589,18 +4597,18 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4630,18 +4638,18 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4671,18 +4679,18 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4712,18 +4720,18 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4753,18 +4761,18 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4794,18 +4802,18 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4835,18 +4843,18 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4876,18 +4884,18 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4917,18 +4925,18 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4958,18 +4966,18 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4999,18 +5007,18 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -5040,18 +5048,18 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -5081,18 +5089,18 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -5122,18 +5130,18 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -5163,18 +5171,18 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -5204,18 +5212,18 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -5245,18 +5253,18 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -5286,18 +5294,18 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -5327,18 +5335,18 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -5368,18 +5376,18 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -5409,18 +5417,18 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -5450,18 +5458,18 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -5491,18 +5499,18 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -5532,18 +5540,18 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -5573,18 +5581,18 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5614,18 +5622,18 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -5655,11 +5663,11 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
@@ -5669,24 +5677,20 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5696,15 +5700,15 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
@@ -5714,24 +5718,20 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5741,28 +5741,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5782,28 +5782,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5823,38 +5823,42 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5864,38 +5868,42 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5905,22 +5913,22 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5950,18 +5958,18 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5991,18 +5999,18 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -6032,18 +6040,18 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -6073,11 +6081,11 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
@@ -6087,24 +6095,20 @@
           <t>충남</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6114,28 +6118,28 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6155,28 +6159,28 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6196,28 +6200,28 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6227,7 +6231,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6237,38 +6241,42 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6278,150 +6286,359 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-130</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>342</v>
+        <v>128</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-342</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>20250929</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>20291001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>1135</v>
+        <v>128</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-1135</t>
+          <t>D-128</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>128</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>D-128</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>128</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>D-128</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>20270129</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>157</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>D-157</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>340</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>D-340</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>울주군</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>국민임대</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>20250929</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>20291001</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>1133</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>D-1133</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H139" t="n">
-        <v>1135</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>D-1135</t>
+      <c r="H144" t="n">
+        <v>1133</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>D-1133</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I144"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>의왕시</t>
+          <t>화천군</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>의왕고천A-1BL[리츠]·안양명학A-1BL 행복주택 예비입주자 모집</t>
+          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,12 +491,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020552&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -511,33 +511,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>수원시 팔달구</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 전세임대주택 입주자모집(제2차)</t>
+          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260819</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;idx=882115&amp;amode=view&amp;cpage=1&amp;stype=title&amp;upunit=50</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -552,17 +556,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>남양주시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -572,17 +576,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -597,17 +601,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>화성시 효행구</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>인천 미추홀구.영종구 행복주택 예비입주자 모집(2026.08.05)</t>
+          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -617,17 +621,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020411&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -642,17 +646,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>고창군</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>고창율계 고령자복지주택(영구임대) 예비입주자 모집</t>
+          <t>경산시 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -662,17 +666,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260825</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020535&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -687,62 +691,62 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>성남시 수정구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>성남금토 A-4블록 신혼희망타운 행복주택 입주자 모집공고</t>
+          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020534&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>금정구</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -752,87 +756,87 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>괴산군</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(대구동구, 대구수성구, 경산시) 청년매입임대주택 예비입주자 모집공고</t>
+          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260828</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020533&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>사상구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>26년 2차 부산 분양전환형 든든전세 입주자 모집 공고</t>
+          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -842,267 +846,267 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020540&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020548&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>정관8 행복주택 예비입주자 모집(완화공고)</t>
+          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020464&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>이천시</t>
+          <t>영도구</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>이천장호원 B2블록 통합공공임대주택 예비입주자 모집공고</t>
+          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020531&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>화천군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
+          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>수원시 팔달구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
+          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
+          <t>원주시지역 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1112,25 +1116,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1146,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
+          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1157,42 +1161,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>경산시 영구임대주택 예비입주자 모집</t>
+          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1202,312 +1206,312 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>금정구</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>괴산군</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
+          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>영도구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1517,47 +1521,47 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1567,42 +1571,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1612,47 +1616,47 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>원주시지역 행복주택 예비입주자 모집</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1662,37 +1666,37 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020626&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1707,37 +1711,37 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
+          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1752,37 +1756,37 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1797,42 +1801,42 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1842,127 +1846,127 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
+          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>양주시</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1972,42 +1976,42 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2017,127 +2021,127 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>의성군</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2152,42 +2156,42 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2197,42 +2201,42 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>김천시</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
+          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2242,87 +2246,87 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
+          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2332,37 +2336,37 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
+          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2372,62 +2376,62 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>구로구</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
+          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260906</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://happydorm.or.kr/gaebong/ko/index</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -2442,17 +2446,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2467,155 +2471,155 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>의성군</t>
+          <t>수원시 권선구</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
+          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>광주시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
@@ -2627,57 +2631,57 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>오산시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>부천시 소사구</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2687,42 +2691,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2732,197 +2736,197 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>부산진구</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
+          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>구로구</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260906</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://happydorm.or.kr/gaebong/ko/index</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -2937,62 +2941,62 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>연제구</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3012,78 +3016,82 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>아산시</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3093,43 +3101,47 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>춘천시</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3139,32 +3151,28 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3179,42 +3187,38 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3224,127 +3228,127 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3364,236 +3368,240 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-17</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-51</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-65</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-66</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>안산시 단원구</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠]경남지역 예비입주자 상시모집</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019919&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-97</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-97</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -3605,171 +3613,175 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-97</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-127</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>익산시</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-18</t>
         </is>
       </c>
     </row>
@@ -3779,137 +3791,149 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>횡성군</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-26</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>청주시 서원구</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-35</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-48</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3919,251 +3943,263 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-62</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-63</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-94</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-94</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-116</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-124</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4173,7 +4209,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4183,28 +4219,28 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4224,28 +4260,28 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4265,28 +4301,28 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4296,7 +4332,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4306,38 +4342,42 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4347,38 +4387,42 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4388,38 +4432,42 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4429,28 +4477,28 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4470,28 +4518,28 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4501,7 +4549,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4511,28 +4559,28 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4552,28 +4600,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4583,7 +4631,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4593,28 +4641,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4634,28 +4682,28 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4665,7 +4713,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4675,28 +4723,28 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4716,28 +4764,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4747,7 +4795,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4757,28 +4805,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4798,28 +4846,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4829,7 +4877,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4839,28 +4887,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4880,28 +4928,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4911,7 +4959,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4921,28 +4969,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4962,28 +5010,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4993,7 +5041,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5003,28 +5051,28 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5044,28 +5092,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5075,7 +5123,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5085,28 +5133,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5126,28 +5174,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5157,7 +5205,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5167,28 +5215,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5208,28 +5256,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5239,7 +5287,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5249,28 +5297,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5290,28 +5338,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5321,7 +5369,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5331,28 +5379,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5372,28 +5420,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5403,7 +5451,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5413,28 +5461,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5454,28 +5502,28 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5485,7 +5533,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5495,28 +5543,28 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5536,28 +5584,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5567,7 +5615,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5577,28 +5625,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5618,28 +5666,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5649,7 +5697,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5659,28 +5707,28 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5700,28 +5748,28 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5731,7 +5779,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5741,28 +5789,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5782,28 +5830,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5813,7 +5861,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5823,42 +5871,38 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5868,42 +5912,38 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5913,22 +5953,22 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5958,18 +5998,18 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5999,18 +6039,18 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -6040,18 +6080,18 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -6081,18 +6121,18 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -6122,18 +6162,18 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -6163,18 +6203,18 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -6204,18 +6244,18 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -6245,38 +6285,38 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6286,38 +6326,42 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6327,28 +6371,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6368,28 +6412,28 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6409,28 +6453,28 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6440,7 +6484,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6450,195 +6494,609 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-128</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-157</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>340</v>
+        <v>125</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-340</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20250929</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>20291001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>1133</v>
+        <v>125</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-1133</t>
+          <t>D-125</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>125</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>D-125</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>125</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>D-125</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>매입임대</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>20260316</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>125</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>D-125</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>125</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>D-125</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>125</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>D-125</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>125</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>D-125</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>125</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>D-125</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>20270129</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>154</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>D-154</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>337</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>D-337</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>울주군</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>국민임대</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>20250929</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>20291001</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>1130</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>D-1130</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H144" t="n">
-        <v>1133</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>D-1133</t>
+      <c r="H154" t="n">
+        <v>1130</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>D-1130</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,62 +466,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>화천군</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>화천신읍2 영구임대주택 예비입주자 모집</t>
+          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020443&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>수원시 팔달구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[수원시]수원시 역세권 새빛 청년존(Zone) 4호 및 1호 예비입주자 모집공고</t>
+          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -531,267 +531,267 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020560&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>남양주시</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>남양주진접2 A-4BL 신혼희망타운 행복주택 최초 입주자 모집공고(‘26.08.13)</t>
+          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260407</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020545&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=39&amp;aisTpCd=42&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>화성시 효행구</t>
+          <t>영도구</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>화성시 행복주택 입주자격완화 예비입주자 모집(26.08.05)</t>
+          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260824</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020511&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>경산시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>경산시 영구임대주택 예비입주자 모집</t>
+          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260825</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020522&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>대구금호6 및 연경숲 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061156&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>금정구</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>부산동부권 집주인 임대주택 입주자 선착순 수시모집 공고(부산금정구)</t>
+          <t>원주시지역 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020526&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=36&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>괴산군</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>괴산미니복합타운A1BL 행복주택 입주자격완화 추가모집공고</t>
+          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -801,62 +801,62 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260828</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020558&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
+          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -871,37 +871,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -916,37 +916,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -961,17 +961,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>영도구</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
+          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1006,22 +1006,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1031,42 +1031,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1076,47 +1076,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>원주시지역 행복주택 예비입주자 모집</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1126,37 +1126,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1171,32 +1171,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1216,37 +1216,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1261,37 +1261,37 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1306,15 +1306,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020626&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1351,37 +1351,37 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1396,37 +1396,37 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1441,42 +1441,42 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1486,127 +1486,127 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>양주시</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1616,42 +1616,42 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,82 +1661,82 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020626&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>의성군</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
+          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1746,47 +1746,47 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
+          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1816,37 +1816,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1861,107 +1861,107 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>김천시</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
+          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>양주시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1971,42 +1971,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2016,42 +2016,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>의성군</t>
+          <t>구로구</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
+          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260906</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://happydorm.or.kr/gaebong/ko/index</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2106,25 +2106,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2136,57 +2136,57 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
+          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>수원시 팔달구</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2196,42 +2196,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>이천시</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2241,242 +2241,238 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>대전</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>동구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>부천시 소사구</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>구로구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20260906</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://happydorm.or.kr/gaebong/ko/index</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -2491,17 +2487,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>부산진구</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2521,32 +2517,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>수원시 권선구</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2566,32 +2562,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>광주시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2611,32 +2607,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>오산시</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2656,42 +2652,42 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>부천시 소사구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2701,32 +2697,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2746,127 +2742,123 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>유성구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>부산</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>부산진구</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2876,42 +2868,38 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>제물포구</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2921,37 +2909,37 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2961,42 +2949,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3006,42 +2994,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3051,17 +3039,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -3076,22 +3064,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3101,12 +3089,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -3126,239 +3114,247 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>김포시</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>안산시 단원구</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3368,42 +3364,42 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3413,167 +3409,167 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-32</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3583,115 +3579,115 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-33</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-46</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-60</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3699,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3718,430 +3714,414 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-61</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-92</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-26</t>
+          <t>D-92</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-35</t>
+          <t>D-114</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-48</t>
+          <t>D-122</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>양산시</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-62</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-63</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-94</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-94</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-116</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
@@ -4153,12 +4133,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4168,25 +4148,25 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-124</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
@@ -4196,20 +4176,24 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4219,28 +4203,28 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4260,28 +4244,28 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4301,28 +4285,28 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4332,7 +4316,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4342,42 +4326,38 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4387,42 +4367,38 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4432,42 +4408,38 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4477,28 +4449,28 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4518,28 +4490,28 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4549,7 +4521,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4559,28 +4531,28 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4600,28 +4572,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4631,7 +4603,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4641,28 +4613,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4682,28 +4654,28 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4713,7 +4685,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4723,28 +4695,28 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4764,28 +4736,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4795,7 +4767,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4805,28 +4777,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4846,28 +4818,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4877,7 +4849,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4887,28 +4859,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4928,28 +4900,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4959,7 +4931,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4969,28 +4941,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5010,28 +4982,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5041,7 +5013,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5051,28 +5023,28 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5092,28 +5064,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5123,7 +5095,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5133,28 +5105,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5174,28 +5146,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5205,7 +5177,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5215,28 +5187,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5256,28 +5228,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5287,7 +5259,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5297,28 +5269,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5338,28 +5310,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5369,7 +5341,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5379,28 +5351,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5420,28 +5392,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5451,7 +5423,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5461,28 +5433,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5502,28 +5474,28 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5533,7 +5505,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5543,28 +5515,28 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5584,28 +5556,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5615,7 +5587,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5625,28 +5597,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5666,28 +5638,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5697,7 +5669,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5707,28 +5679,28 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5748,28 +5720,28 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5779,7 +5751,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5789,28 +5761,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5830,28 +5802,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5861,7 +5833,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5871,28 +5843,28 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5912,28 +5884,28 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5943,7 +5915,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5953,28 +5925,28 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5994,28 +5966,28 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6025,7 +5997,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6035,38 +6007,42 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6076,38 +6052,42 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6117,22 +6097,22 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -6162,18 +6142,18 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -6203,18 +6183,18 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -6244,18 +6224,18 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -6285,38 +6265,34 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6326,42 +6302,38 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6371,28 +6343,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6412,28 +6384,28 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6443,7 +6415,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6453,38 +6425,42 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6494,28 +6470,28 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6525,7 +6501,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6535,28 +6511,28 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6576,28 +6552,28 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6617,28 +6593,28 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6648,7 +6624,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6658,445 +6634,195 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-123</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270129</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-152</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260812</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270731</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>125</v>
+        <v>335</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-335</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>125</v>
+        <v>1128</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>D-125</t>
+          <t>D-1128</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>125</v>
+        <v>1128</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>D-125</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H149" t="n">
-        <v>125</v>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>D-125</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H150" t="n">
-        <v>125</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>D-125</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>20270129</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H151" t="n">
-        <v>154</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>D-154</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>20260812</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>20270731</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H152" t="n">
-        <v>337</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>D-337</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H153" t="n">
-        <v>1130</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>D-1130</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H154" t="n">
-        <v>1130</v>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>D-1130</t>
+          <t>D-1128</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,127 +466,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 고령군 일반 매입임대주택 입주자 및 예비입주자 모집공고</t>
+          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=71b78e43-bfa5-4898-b485-aa19b3e548fb&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(신혼신생아 매입임대주택Ⅰ) 입주자 및 예비입주자 모집공고</t>
+          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=ac988257-4e4a-42f1-a278-7624625547be&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 고령군 임대지원주택(청년 매입임대주택) 입주자 및 예비입주자 모집공고</t>
+          <t>원주시지역 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260407</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=5e372ee0-46dc-458c-85bb-d04efe3315d6&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -601,37 +601,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>영도구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 영구임대주택 예비입주자 (수시)모집공고</t>
+          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260824</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800611</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -646,22 +646,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -671,37 +671,37 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -716,37 +716,37 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>원주시지역 행복주택 예비입주자 모집</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -766,37 +766,37 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -856,37 +856,37 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -901,37 +901,37 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -946,15 +946,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -991,15 +991,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1011,17 +1011,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1036,15 +1036,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1081,15 +1081,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1126,15 +1126,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020626&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1171,37 +1171,37 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1216,37 +1216,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1261,42 +1261,42 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1306,127 +1306,127 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020626&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>양주시</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
+          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
+          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1436,82 +1436,82 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
+          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>의성군</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
+          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1531,42 +1531,42 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>양주시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
+          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1576,37 +1576,37 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1616,20 +1616,20 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1641,17 +1641,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,20 +1661,20 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
@@ -1686,57 +1686,57 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>의성군</t>
+          <t>구미시</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
+          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1751,47 +1751,47 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
+          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1801,42 +1801,42 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1846,52 +1846,52 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>김천시</t>
+          <t>구로구</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
+          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260906</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://happydorm.or.kr/gaebong/ko/index</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1906,17 +1906,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1926,197 +1926,193 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
+          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>수원시 팔달구</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
+          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>구로구</t>
+          <t>이천시</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260906</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://happydorm.or.kr/gaebong/ko/index</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>서귀포시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2136,12 +2132,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>부천시 소사구</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2161,15 +2157,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2177,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>수원시 팔달구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2206,15 +2202,15 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2222,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>이천시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2251,28 +2247,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>유성구</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2292,32 +2292,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>부천시 소사구</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2337,32 +2337,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2382,32 +2382,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2427,32 +2427,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>유성구</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2472,42 +2472,42 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>부산진구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
+          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2517,32 +2517,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>제물포구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2562,122 +2562,118 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>익산시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2687,47 +2683,43 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>아산시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2737,47 +2729,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2787,42 +2779,42 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2832,28 +2824,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2868,38 +2864,42 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2909,137 +2909,137 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3049,37 +3049,37 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3094,37 +3094,37 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3139,37 +3139,37 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3184,42 +3184,42 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3229,60 +3229,60 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -3294,445 +3294,445 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-12</t>
+          <t>D-30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-16</t>
+          <t>D-30</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-24</t>
+          <t>D-31</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>태백철암1 국민임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020638&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-32</t>
+          <t>D-43</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-33</t>
+          <t>D-44</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-46</t>
+          <t>D-58</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-60</t>
+          <t>D-59</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-61</t>
+          <t>D-90</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3769,15 +3769,15 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-92</t>
+          <t>D-90</t>
         </is>
       </c>
     </row>
@@ -3789,85 +3789,85 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-92</t>
+          <t>D-112</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-114</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
@@ -3877,42 +3877,38 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-122</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3921,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3945,15 +3941,15 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3962,7 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3986,15 +3982,15 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4003,7 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4017,7 +4013,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4027,15 +4023,15 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4045,20 +4041,24 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4068,15 +4068,15 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4113,15 +4113,15 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4133,12 +4133,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4158,42 +4158,38 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4203,15 +4199,15 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4220,7 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4244,15 +4240,15 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4261,7 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4285,15 +4281,15 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4302,7 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4316,7 +4312,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4326,28 +4322,28 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4357,7 +4353,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4367,15 +4363,15 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4384,7 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4408,15 +4404,15 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4425,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4449,15 +4445,15 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4466,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4480,7 +4476,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4490,28 +4486,28 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4521,7 +4517,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4531,15 +4527,15 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4548,7 @@
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4572,15 +4568,15 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4589,7 @@
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4613,15 +4609,15 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4630,7 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4644,7 +4640,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4654,28 +4650,28 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4685,7 +4681,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4695,15 +4691,15 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4712,7 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4736,15 +4732,15 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4753,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4777,15 +4773,15 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4794,7 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4808,7 +4804,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4818,28 +4814,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4849,7 +4845,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4859,15 +4855,15 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4876,7 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4900,15 +4896,15 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4917,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4941,15 +4937,15 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4958,7 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4972,7 +4968,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4982,28 +4978,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5013,7 +5009,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5023,15 +5019,15 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5040,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5064,15 +5060,15 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5081,7 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5105,15 +5101,15 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5122,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5136,7 +5132,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5146,28 +5142,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5177,7 +5173,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5187,15 +5183,15 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5204,7 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5228,15 +5224,15 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5245,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5269,15 +5265,15 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5286,7 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5300,7 +5296,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5310,28 +5306,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5341,7 +5337,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5351,15 +5347,15 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5368,7 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5392,15 +5388,15 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5409,7 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5433,15 +5429,15 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5450,7 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5464,7 +5460,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5474,28 +5470,28 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5505,7 +5501,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5515,15 +5511,15 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5532,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5556,15 +5552,15 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5573,7 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5597,15 +5593,15 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5614,7 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5628,7 +5624,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5638,28 +5634,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5669,7 +5665,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5679,15 +5675,15 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5696,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5720,15 +5716,15 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5737,7 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5761,15 +5757,15 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5778,7 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5792,7 +5788,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5802,28 +5798,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5833,7 +5829,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5843,15 +5839,15 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5860,7 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5884,15 +5880,15 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5901,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5925,15 +5921,15 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5942,7 @@
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5956,7 +5952,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5966,15 +5962,15 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -5984,20 +5980,24 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6007,15 +6007,15 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6027,12 +6027,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>전주시 완산구</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6052,42 +6052,38 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6097,15 +6093,15 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6114,7 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6138,15 +6134,15 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6155,7 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6179,15 +6175,15 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6196,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6210,7 +6206,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6220,28 +6216,28 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6251,7 +6247,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6261,15 +6257,15 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6278,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6302,15 +6298,15 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6319,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6343,15 +6339,15 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6360,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6374,7 +6370,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6384,15 +6380,15 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6402,20 +6398,24 @@
           <t>충남</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6425,42 +6425,38 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6470,15 +6466,15 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6487,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6511,15 +6507,15 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6528,7 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6552,15 +6548,15 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6569,7 @@
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6583,7 +6579,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6593,73 +6589,77 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-121</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270129</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-123</t>
+          <t>D-150</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6669,42 +6669,42 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260812</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20270731</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>152</v>
+        <v>333</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>D-152</t>
+          <t>D-333</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>울주군</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6714,25 +6714,25 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>335</v>
+        <v>1126</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>D-335</t>
+          <t>D-1126</t>
         </is>
       </c>
     </row>
@@ -6769,60 +6769,15 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>D-1128</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
-        <v>1128</v>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>D-1128</t>
+          <t>D-1126</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>원주시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>군산금암 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>원주시지역 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -511,17 +511,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>군산내흥7 행복주택 예비입주자 모집 공고(26.08.18)</t>
+          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020569&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -556,27 +556,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>원주시지역 행복주택 예비입주자 모집</t>
+          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -586,32 +586,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -631,37 +631,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
+          <t>서울번동3 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -676,37 +676,37 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -721,37 +721,37 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -766,15 +766,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
+          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -856,15 +856,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -901,15 +901,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -946,15 +946,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -991,15 +991,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1036,15 +1036,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020626&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>검단구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1081,37 +1081,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1126,37 +1126,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020626&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1171,42 +1171,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>음성군</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
+          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1216,52 +1216,52 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>오늘 마감</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
+          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1276,37 +1276,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>양주시</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
+          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1321,17 +1321,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
+          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1351,42 +1351,42 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>양주시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
+          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1396,32 +1396,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>의성군</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1486,52 +1486,52 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>의성군</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
+          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1546,37 +1546,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1591,22 +1591,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>구미시</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
+          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1621,42 +1621,42 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1666,42 +1666,42 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>구미시</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
+          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1711,32 +1711,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>구로구</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
+          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1791,42 +1791,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260906</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://happydorm.or.kr/gaebong/ko/index</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1836,115 +1836,115 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>구로구</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
+          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260906</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://happydorm.or.kr/gaebong/ko/index</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>수원시 영통구</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -1954,14 +1954,10 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>안성시</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1981,15 +1977,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -1999,14 +1995,10 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>수원시 팔달구</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,15 +2018,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>이천시</t>
+          <t>부천시 소사구</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2071,15 +2063,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2089,10 +2081,14 @@
           <t>경기</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>부천시 원미구</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2112,15 +2108,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2128,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>부천시 소사구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2157,15 +2153,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2178,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2202,32 +2198,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2247,32 +2243,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>유성구</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2292,32 +2288,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2337,15 +2333,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2353,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>제물포구</t>
+          <t>미추홀구</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2382,15 +2378,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2403,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2427,15 +2423,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2476,11 +2472,11 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2521,11 +2517,11 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
@@ -2566,73 +2562,73 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
+          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2647,84 +2643,92 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>청주시 흥덕구</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>춘천시</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2734,42 +2738,42 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
+          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2779,42 +2783,38 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>제주시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2824,32 +2824,28 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2864,137 +2860,137 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3004,32 +3000,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3039,7 +3035,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3049,37 +3045,37 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3094,42 +3090,42 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3139,42 +3135,42 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3184,32 +3180,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3219,7 +3215,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3229,510 +3225,510 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-22</t>
+          <t>D-9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-30</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-30</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>예산군</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-31</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>서산시</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>태백철암1 국민임대주택 예비입주자 모집 공고</t>
+          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020638&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-43</t>
+          <t>D-15</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-44</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-58</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-59</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-90</t>
+          <t>D-21</t>
         </is>
       </c>
     </row>
@@ -3742,14 +3738,10 @@
           <t>경북</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3759,25 +3751,25 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-90</t>
+          <t>D-29</t>
         </is>
       </c>
     </row>
@@ -3789,339 +3781,355 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-112</t>
+          <t>D-29</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-30</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>당진시</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-43</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>양산시</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-57</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-58</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-89</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-89</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-111</t>
         </is>
       </c>
     </row>
@@ -4133,12 +4141,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>태백시</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4148,32 +4156,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -4203,18 +4211,18 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -4244,18 +4252,18 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4285,18 +4293,18 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4326,34 +4334,38 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4363,38 +4375,42 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4404,38 +4420,42 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4445,28 +4465,28 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4476,7 +4496,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4486,28 +4506,28 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4527,28 +4547,28 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4568,28 +4588,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4599,7 +4619,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4609,28 +4629,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4640,7 +4660,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4650,28 +4670,28 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4691,28 +4711,28 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4732,28 +4752,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4763,7 +4783,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4773,28 +4793,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4804,7 +4824,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4814,28 +4834,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4855,28 +4875,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4896,28 +4916,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4927,7 +4947,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4937,28 +4957,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4968,7 +4988,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4978,28 +4998,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5019,28 +5039,28 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5060,28 +5080,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5091,7 +5111,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5101,28 +5121,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5132,7 +5152,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5142,28 +5162,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5183,28 +5203,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5224,28 +5244,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5255,7 +5275,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5265,28 +5285,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5296,7 +5316,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5306,28 +5326,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5347,28 +5367,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5388,28 +5408,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5419,7 +5439,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5429,28 +5449,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5460,7 +5480,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5470,28 +5490,28 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5511,28 +5531,28 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5552,28 +5572,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5583,7 +5603,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5593,28 +5613,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5624,7 +5644,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5634,28 +5654,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5675,28 +5695,28 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5716,28 +5736,28 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5747,7 +5767,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5757,28 +5777,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5788,7 +5808,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5798,28 +5818,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5839,28 +5859,28 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5880,28 +5900,28 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5911,7 +5931,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5921,28 +5941,28 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5952,7 +5972,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5962,42 +5982,38 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>김제시</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6007,42 +6023,38 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6052,28 +6064,28 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6083,7 +6095,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6093,28 +6105,28 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6134,28 +6146,28 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6175,28 +6187,28 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6206,7 +6218,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6216,28 +6228,28 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6247,7 +6259,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6257,38 +6269,42 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6298,38 +6314,42 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6339,28 +6359,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6370,7 +6390,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6380,42 +6400,38 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20260316</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6425,28 +6441,28 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6466,28 +6482,28 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6497,7 +6513,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6507,28 +6523,28 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6548,28 +6564,28 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6579,7 +6595,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6589,195 +6605,486 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-121</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>20270129</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-150</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>20260812</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>20270731</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>333</v>
+        <v>120</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>D-333</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>울주군</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>20250929</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>20291001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1126</v>
+        <v>120</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>D-1126</t>
+          <t>D-120</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>120</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>D-120</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>120</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>D-120</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>120</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>D-120</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>전세임대</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>20261231</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>120</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>D-120</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>20270129</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>149</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>D-149</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>20260812</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>20270731</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>332</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>D-332</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>울주군</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>국민임대</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>20250929</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>20291001</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>1125</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>D-1125</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>국민임대</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>20250929</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>20291001</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
         <is>
           <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
-      <c r="H147" t="n">
-        <v>1126</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>D-1126</t>
+      <c r="H154" t="n">
+        <v>1125</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>D-1125</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>원주시</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>원주시지역 행복주택 예비입주자 모집</t>
+          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -491,12 +491,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -516,32 +516,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>파주시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>부천영상 지역전략산업지원 행복주택 예비입주자 모집공고(‘26.08.18)</t>
+          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -556,22 +556,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>평택고덕A-58블록 고령자복지주택(영구임대) 예비입주자 모집(2026.08.20)</t>
+          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020600&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -601,17 +601,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020605&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -646,17 +646,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>의성군</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>서울번동3 행복주택 예비입주자 모집</t>
+          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020577&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -691,37 +691,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 인천광역시 영구임대주택 예비입주자 모집(인천갈산2)</t>
+          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020599&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -736,22 +736,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -761,42 +761,42 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020607&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 국민임대 최초 입주자 모집</t>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -806,42 +806,42 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020604&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>구미시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -851,222 +851,222 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020608&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>인천검단 AA19블록 영구임대 최초 입주자 모집</t>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020602&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020596&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>인천서창1단지 영구임대주택 예비입주자 모집 공고</t>
+          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020583&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>구로구</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260906</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020626&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://happydorm.or.kr/gaebong/ko/index</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인천시 검단지역 영구임대주택 예비입주자 모집공고(2026.08.20)</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1076,82 +1076,82 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020595&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>천안아산 대학생,청년 행복주택 자격완화 예비입주자 모집 (2026.08.18)</t>
+          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020513&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>용인시 기흥구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[충북지역본부] 든든전세주택 입주자 모집공고(비분양전환)</t>
+          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1161,115 +1161,115 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020571&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>광명시</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>음성금왕1 50년공공임대주택 예비입주자 모집 공고[2026.08.21]</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020567&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>오늘 마감</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>수원시 팔달구</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>양주시</t>
+          <t>부천시 오정구</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1296,267 +1296,267 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>의성군</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
+          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>연수구</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1566,42 +1566,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>구미시</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1611,115 +1611,115 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>서해구</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
@@ -1731,102 +1731,102 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
+          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>구로구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20260906</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://happydorm.or.kr/gaebong/ko/index</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1836,52 +1836,52 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020676&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1891,42 +1891,42 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020672&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>수원시 영통구</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1936,38 +1936,42 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>진천군</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
+          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1977,38 +1981,42 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>청주시 흥덕구</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2018,42 +2026,42 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020671&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>부천시 소사구</t>
+          <t>청주시 흥덕구</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2063,52 +2071,52 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2123,37 +2131,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2168,22 +2176,18 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>부천시 원미구</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2193,12 +2197,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2213,22 +2217,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>대전</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>유성구</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2258,17 +2258,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2278,17 +2278,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2303,17 +2303,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -2348,22 +2348,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2373,42 +2373,42 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2418,42 +2418,42 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2463,282 +2463,282 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>청주시 흥덕구</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2753,37 +2753,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -2798,33 +2798,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>서귀포시</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -2839,33 +2843,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>서귀포시</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -2880,540 +2888,536 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
+          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>예산군</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>양산사송 A-8BL 영구임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020658&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>서산시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-18</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-18</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>대구</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>달서구</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>경주시</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-29</t>
         </is>
       </c>
     </row>
@@ -3425,130 +3429,130 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-42</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>예산군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-56</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>서산시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-57</t>
         </is>
       </c>
     </row>
@@ -3560,40 +3564,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-88</t>
         </is>
       </c>
     </row>
@@ -3605,40 +3609,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>칠곡군</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-88</t>
         </is>
       </c>
     </row>
@@ -3650,40 +3654,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>포항시 남구</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-110</t>
         </is>
       </c>
     </row>
@@ -3695,233 +3699,221 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20260923</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-29</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>경주시</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-29</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>청주시 서원구</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-30</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-43</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3931,242 +3923,230 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-57</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-58</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>태백시</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-89</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>칠곡군</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-89</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경북</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>포항시 남구</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-111</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261231</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -4181,13 +4161,13 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4197,7 +4177,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4207,28 +4187,28 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4248,28 +4228,28 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4289,28 +4269,28 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4320,7 +4300,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4330,42 +4310,38 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4375,42 +4351,38 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4420,42 +4392,38 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4465,28 +4433,28 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4506,28 +4474,28 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4537,7 +4505,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4547,28 +4515,28 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4588,28 +4556,28 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4619,7 +4587,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4629,28 +4597,28 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4670,28 +4638,28 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4701,7 +4669,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4711,28 +4679,28 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4752,28 +4720,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4783,7 +4751,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4793,28 +4761,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4834,28 +4802,28 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4865,7 +4833,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4875,28 +4843,28 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4916,28 +4884,28 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4947,7 +4915,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4957,28 +4925,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4998,28 +4966,28 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5029,7 +4997,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5039,28 +5007,28 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5080,28 +5048,28 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5111,7 +5079,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5121,28 +5089,28 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5162,28 +5130,28 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5193,7 +5161,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5203,28 +5171,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5244,28 +5212,28 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5275,7 +5243,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5285,28 +5253,28 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5326,28 +5294,28 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5357,7 +5325,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5367,28 +5335,28 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5408,28 +5376,28 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5439,7 +5407,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5449,28 +5417,28 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5490,28 +5458,28 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5521,7 +5489,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5531,28 +5499,28 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5572,28 +5540,28 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5603,7 +5571,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5613,28 +5581,28 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5654,28 +5622,28 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5685,7 +5653,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5695,28 +5663,28 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5736,28 +5704,28 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>세종</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5767,7 +5735,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5777,28 +5745,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5818,28 +5786,28 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5849,7 +5817,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5859,38 +5827,42 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>김제시</t>
+        </is>
+      </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260101</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5900,38 +5872,42 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>전주시 완산구</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260303</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5941,22 +5917,22 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5986,18 +5962,18 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -6027,18 +6003,18 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -6068,18 +6044,18 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -6109,18 +6085,18 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -6150,18 +6126,18 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -6191,18 +6167,18 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -6232,18 +6208,18 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -6273,38 +6249,38 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>김제검산1단지 영구임대주택 예비입주자 모집 공고(상시모집)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20260101</t>
+          <t>20260316</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6314,42 +6290,38 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019412&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>전주시(전주평화1,전주평화4) 영구임대주택 예비입주자 모집 공고(공고일:2026.02.10.)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20260303</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6359,28 +6331,28 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019241&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6400,28 +6372,28 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6441,28 +6413,28 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6472,7 +6444,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6482,609 +6454,195 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-119</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>삼척시</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270129</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-148</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260812</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20270731</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>120</v>
+        <v>331</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-331</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>120</v>
+        <v>1124</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>D-120</t>
+          <t>D-1124</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>울주군</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20250929</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20291001</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>120</v>
+        <v>1124</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>D-120</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>120</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>D-120</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>당진시</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>매입임대</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019433&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>120</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>D-120</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H147" t="n">
-        <v>120</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>D-120</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
-        <v>120</v>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>D-120</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H149" t="n">
-        <v>120</v>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>D-120</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>전세임대</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>20261231</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H150" t="n">
-        <v>120</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>D-120</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>삼척시</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>삼척도계·정선신동 국민임대주택 예비입주자 입주자격완화 공고</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>20260915</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>20270129</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020581&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H151" t="n">
-        <v>149</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>D-149</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>군산시 국민임대주택 입주자 선착순 상시 모집(경암부향 등 7개 단지)</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>20260812</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>20270731</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020453&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H152" t="n">
-        <v>332</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>D-332</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018799&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H153" t="n">
-        <v>1125</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>D-1125</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>울주군</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>울산광역시 국민임대주택 예비입주자 정례모집 공고(2025.09.15.)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>국민임대</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>20250929</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>20291001</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300018780&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
-        </is>
-      </c>
-      <c r="H154" t="n">
-        <v>1125</v>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>D-1125</t>
+          <t>D-1124</t>
         </is>
       </c>
     </row>

--- a/housing_notices.xlsx
+++ b/housing_notices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I144"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,37 +466,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>강릉시</t>
+          <t>평택시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(26.8.18)강릉시·삼척시·정선군 행복주택 예비입주자 모집</t>
+          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020542&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -511,17 +511,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>파주시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[경기북부] 2026년 3차 비분양전환형 든든전세주택 입주자 모집공고</t>
+          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -531,17 +531,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020553&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -556,22 +556,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>김천시</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>경남 고성서외 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020574&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -601,17 +601,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>경남 진주가좌(경상국립대) 행복주택 예비입주자 모집(26.08.18.)</t>
+          <t>낭월 다가온 청년주택 추가모집 공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020575&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -646,17 +646,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>의성군</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>경북서부권 김천시, 의성군 행복주택 예비입주자 모집</t>
+          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260902</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020570&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -696,12 +696,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>익산인화 행복주택 입주자격완화 예비입주자 모집 공고(26.08.18)</t>
+          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20260903</t>
+          <t>20260904</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020554&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -736,67 +736,67 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>평택시</t>
+          <t>구로구</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>평택시 지역 영구임대주택 예비입주자 모집(2026.08.19)</t>
+          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260906</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020564&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://happydorm.or.kr/gaebong/ko/index</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>경남 밀양시 일반 매입임대주택 예비입주자 모집공고</t>
+          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -806,37 +806,37 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020547&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>구미시</t>
+          <t>안성시</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[경상북도 구미시, 김천시] 매입임대주택 예비입주자 모집공고</t>
+          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -846,250 +846,246 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020568&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>낭월 다가온 청년주택 추가모집 공고</t>
+          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.dcco.kr/web/board/list.do?mId=43</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>수원시 팔달구</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(2026.08.19.) 전주덕진 행복주택 예비입주자 모집</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020579&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>완주군</t>
-        </is>
-      </c>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(2026.08.19.)완주삼봉(A-1,A-3BL) 행복주택 자격완화 예비입주자 모집</t>
+          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20260904</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020580&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>구로구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>기숙사형 청년주택(개봉동) 2026학년도 2학기 상시 입사생 모집 공고</t>
+          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260820</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20260906</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://happydorm.or.kr/gaebong/ko/index</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>제주지역 행복주택 예비입주자 모집(2026.08.18.)</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020582&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1097,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>안성시</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[경기 안성시] 26년 2차 기숙사형 청년주택 예비입주자 모집공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1126,15 +1122,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020618&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1142,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>용인시 기흥구</t>
+          <t>부천시 원미구</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[경기남부] 26년 3차 청년 매입임대주택 예비입주자 모집공고</t>
+          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1171,32 +1167,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020621&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>광명시</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅰ 예비입주자 모집공고</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1216,32 +1212,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020628&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>수원시 팔달구</t>
+          <t>사상구</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[경기남부] 신혼·신생아 매입임대주택Ⅱ(전세형) 예비입주자 모집공고</t>
+          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1261,27 +1257,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020629&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>부천시 오정구</t>
+          <t>연수구</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1310,23 +1306,23 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1355,23 +1351,23 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>제물포구</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1400,23 +1396,23 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>부천시 원미구</t>
+          <t>서해구</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1445,38 +1441,38 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>유성구</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1486,32 +1482,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>부산</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년 장기미임대 매입임대주택 (예비)입주자 모집 공고</t>
+          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1531,42 +1527,42 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.bmc.busan.kr/board/view.do?boardId=BBS_0000004&amp;menuCd=DOM_000000101001003000&amp;orderBy=DATA_SID%20DESC&amp;paging=ok&amp;startPage=1&amp;dataSid=800624</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>연수구</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[인천지역본부] 26년 6차 청년 매입임대주택 예비입주자 모집공고(인천,부천)</t>
+          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1576,42 +1572,42 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020630&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020676&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅰ 예비입주자 모집공고(인천,부천)</t>
+          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1621,42 +1617,42 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020634&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020672&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>제물포구</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1666,42 +1662,42 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020661&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>서해구</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[인천지역본부]26년 6차 신혼·신생아Ⅱ(전세형) 예비입주자 모집공고(인천,부천)</t>
+          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1711,37 +1707,37 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020633&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>청주시 흥덕구</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>익산시(익산부송1, 익산동산)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1756,42 +1752,42 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020603&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020685&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>청주시 흥덕구</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[대전·충남] 2026년 2차 든든전세주택 입주자 모집공고(비분양전환형)</t>
+          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1801,15 +1797,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020620&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020671&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1817,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>청주시 흥덕구</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
+          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1846,52 +1842,52 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020676&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
+          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260831</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020672&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -1906,22 +1902,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>진천군</t>
+          <t>고령군</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>진천성석,진천이월,청주우암 행복주택(입주자격완화) 예비입주자 추가모집</t>
+          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1931,12 +1927,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020646&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1951,37 +1947,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>진천군</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>진천이월 국민임대주택 예비입주자 모집(소득 및 자산요건배제, 무주택요건 완화)</t>
+          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020648&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -1996,37 +1988,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>청주시 흥덕구</t>
-        </is>
-      </c>
+          <t>세종</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
+          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020671&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2041,37 +2029,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>청주시 흥덕구</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>청주산단1,청주산단2 행복주택 예비입주자 모집</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020647&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2086,27 +2074,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>춘천시</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>춘천 산수빌 국민임대아파트 예비 입주자 모집안내</t>
+          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2116,52 +2104,52 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.gdco.co.kr/customer/notice_view.php?intSeq=5805&amp;strBoardID=NOTI&amp;page=1&amp;pageSize=10</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>고령군</t>
+          <t>동해시</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>고령디오팰리스 국민임대주택 입주자격완화 예비입주자 모집</t>
+          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260907</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020615&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2176,18 +2164,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 세종시 영구임대주택(도램마을7‧8단지) 입주자 및 예비입주자 모집 공고</t>
+          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2197,12 +2189,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12843</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2217,18 +2209,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>세종 신흥사랑주택 입주자 15차 모집 공고</t>
+          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2238,12 +2234,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardArticle.do?nttId=12845&amp;kind=&amp;mno=sitemap_02&amp;pageIndex=1&amp;searchCnd=0&amp;searchWrd=%EC%9E%85%EC%A3%BC%EC%9E%90+%EB%AA%A8%EC%A7%91</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2258,37 +2254,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>김포시</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (서귀포시)</t>
+          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2303,37 +2299,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>[제주지역본부] 신혼.신생아 매입임대주택Ⅰ 예비입주자 모집 공고 (제주시)</t>
+          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260826</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020622&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.ansanuc.net</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -2348,17 +2344,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(영구임대) 입주자 모집</t>
+          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2378,37 +2374,37 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020609&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>안동시</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>동해천곡 고령자복지주택(행복주택) 입주자 모집</t>
+          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2423,42 +2419,42 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020610&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>달서구</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>동해천곡(고령자) 행복주택 입주자 모집</t>
+          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2468,42 +2464,42 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020611&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>김포시</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>김포한강 Ac-05블록 10년 공공임대주택(리츠) 예비입주자 모집 공고</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10년임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2513,42 +2509,42 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061160&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>안산시 단원구</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>안산 선부동 행복주택 예비입주자(청년) 모집 공고</t>
+          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260826</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2558,42 +2554,42 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://apply.ansanuc.net</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>김해구산1 영구임대주택 예비입주자 모집 공고</t>
+          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2603,42 +2599,42 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020500&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>안동시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[안동옥동2] 영구임대주택 예비입주자 모집</t>
+          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2648,32 +2644,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020584&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>대구</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>달서구</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>대구가람1단지 50년 공공임대 예비입주자 모집</t>
+          <t>남원노암 공공임대 50년 예비입주자 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2683,25 +2679,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020573&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020681&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -2713,40 +2709,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020666&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
@@ -2758,167 +2754,167 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>정읍시(정읍수성1)영구임대주택 입주자격완화 예비입주자 모집공고</t>
+          <t>익산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020639&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020636&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 제주특별자치도개발공사 일반 매입임대주택 예비입주자 모집 공고</t>
+          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24135</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>예산군</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>제주특별자치도개발공사 다자녀 매입임대주택 예비입주자 모집 공고</t>
+          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.jpdc.co.kr/open/news/notice.htm?act=view&amp;seq=24134</t>
+          <t>https://apply.cndc.kr/</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>D-8</t>
+          <t>D-11</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>익산부송3단지 50년 공공임대 예비입주자 모집</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아1 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020624&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020675&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -2933,37 +2929,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>강릉시</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택 매입임대 예비입주자 모집(천안, 보령, 서산)</t>
+          <t>[강원지역본부] 26년 3차 신혼신생아2(전세형) 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020679&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -2978,37 +2974,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>예산군</t>
+          <t>춘천시</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 하반기 충남형 행복주택(꿈비채) 예비입주자 모집 공고문(당진, 천안, 예산)</t>
+          <t>[강원지역본부] 26년 3차 청년 매입임대주택 예비자 모집공고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://apply.cndc.kr/</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020673&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -3057,38 +3053,38 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>서산시</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
+          <t>군산시 국민임대주택 예비입주자 모집 공고(26.09.03)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>50년임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3098,105 +3094,105 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020663&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>서산시</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>포항창포 영구임대아파트 예비입주자 모집</t>
+          <t>서산석림3단지 50년공공임대주택 예비입주자 모집공고(2026.09.01.)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>50년임대</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020657&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>포항시 북구</t>
+          <t>안산시 단원구</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>포항학산 영구임대아파트 예비입주자 모집</t>
+          <t>안산 선부동 행복주택 예비입주자(주거급여)모집 공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260903</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20260918</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://www.ansanuc.net/homenew/12286/20328/bbsList.do</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D-18</t>
+          <t>D-14</t>
         </is>
       </c>
     </row>
@@ -3208,85 +3204,85 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
+          <t>포항창포 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>20260922</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020651&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>D-19</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>횡성군</t>
+          <t>포항시 북구</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>강원횡성 통합공공임대주택 입주자 모집</t>
+          <t>포항학산 영구임대아파트 예비입주자 모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>통합공공임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>20260921</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>20260923</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020650&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D-20</t>
+          <t>D-17</t>
         </is>
       </c>
     </row>
@@ -3296,105 +3292,109 @@
           <t>경북</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>경주시</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>경주시, 영천시, 포항시 부도매입(국민임대)주택 입주자격완화 모집공고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260922</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020635&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D-28</t>
+          <t>D-18</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>경주시</t>
+          <t>횡성군</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
+          <t>강원횡성 통합공공임대주택 입주자 모집</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>통합공공임대</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260921</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260923</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020627&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=48&amp;mi=1026</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>D-28</t>
+          <t>D-19</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>충북</t>
+          <t>경북</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>청주시 서원구</t>
+          <t>경산시</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3404,155 +3404,151 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>D-29</t>
+          <t>D-25</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>대구</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
+          <t>대구혁신10, 경산하양3 행복주택 입주자격완화 선계약 후검증 동호지정 입주자 모집</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260810</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020682&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>D-42</t>
+          <t>D-25</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>부산</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
+          <t>부산만덕5 2블록 10년 분양전환공공임대주택(e편한세상 금정산) 예비입주자 모집공고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>10년임대</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20261029</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=0000061163&amp;ccrCnntSysDsCd=02&amp;uppAisTpCd=06&amp;aisTpCd=08&amp;mi=1026</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>D-56</t>
+          <t>D-26</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>군산시</t>
-        </is>
-      </c>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>영구임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020654&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>D-57</t>
+          <t>D-27</t>
         </is>
       </c>
     </row>
@@ -3564,12 +3560,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>영천시</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
+          <t>[경북 포항,경주,영천] 일반 매입임대 입주자 모집공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3579,132 +3575,132 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261001</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020601&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D-88</t>
+          <t>D-27</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>칠곡군</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
+          <t>청주산남2-1 영구임대주택 예비입주자 모집 공고(2026.08.28)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>매입임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20261130</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020625&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D-88</t>
+          <t>D-28</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>포항시 남구</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
+          <t>[청년신혼부부매입임대리츠주택] 충남당진 송산청광플러스원 입주자격완화 상시모집</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>행복주택</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260810</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>20261222</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020529&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=26&amp;mi=1026</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>D-110</t>
+          <t>D-41</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>경남</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>삼척시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
+          <t>양산 사송A-4BL 국민임대주택(29A형)선착순 동호지정 모집(입주자격완화, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3714,189 +3710,205 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20261230</t>
+          <t>20261029</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020495&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>D-118</t>
+          <t>D-55</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>군산시</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>군산신역세권A3(내흥3) 영구임대주택 입주자 추가모집</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>영구임대</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019841&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=09&amp;mi=1026</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-56</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(신혼·신생아 매입임대주택Ⅰ) 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=e54448a5-4c8c-4c3d-bfcf-bc465f677408&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-87</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>칠곡군</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 칠곡군 천원주택(청년 매입임대주택) 입주자 및 예비입주자 모집 공고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>매입임대</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261130</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://www.gbdc.co.kr/boardview/boardview.do?seqId=0000003638&amp;BBS_ID=4c9b3e75-2935-4bcd-96be-62fb07903949&amp;IPDS_IDX=2e8989e9-02ae-48be-9591-f3c4c8e7fa39&amp;BBS_TYPE=L&amp;COLM1=notice&amp;COLM1_CD=notice_02&amp;COLM1_STATUS=&amp;SEARCH_CONTITION=CPDS_SUBJECT_CONTENT&amp;SEARCH_KEYWORD=&amp;CURRENT_PAGE=1</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-87</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>경북</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>포항시 남구</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>포항블루밸리 행복주택 선착순 동호지정 상시모집(입주자격 완화, 통합공임 일반계층 추가, 선계약 후검증)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>행복주택</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261222</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020042&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=10&amp;mi=1026</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-109</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3920,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>동해시</t>
+          <t>삼척시</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>삼척시·정선군 국민임대 예비입주자 상시모집(26.6.10)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3923,25 +3935,25 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>20261231</t>
+          <t>20261230</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300020090&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-117</t>
         </is>
       </c>
     </row>
@@ -3951,24 +3963,20 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>동해시</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3978,15 +3986,15 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
@@ -3996,24 +4004,20 @@
           <t>강원</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>태백시</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>국민임대</t>
+          <t>전세임대</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20260212</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4023,28 +4027,28 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4064,28 +4068,28 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4095,7 +4099,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4105,38 +4109,42 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4146,38 +4154,42 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019312&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>동해시</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>동해유성,태백철암장미 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4187,38 +4199,42 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019308&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>경남</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>태백시</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>태백궁전 국민임대 입주자격완화 예비입주자 상시모집(26.02.02 공고)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>전세임대</t>
+          <t>국민임대</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260212</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4228,28 +4244,28 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019307&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=06&amp;aisTpCd=07&amp;mi=1026</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
+          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4269,28 +4285,28 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
+          <t>2026년 신혼·신생아 전세임대 I 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4310,28 +4326,28 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019550&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경남</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
+          <t>2026년 신혼·신생아 전세임대Ⅱ 입주자 수시모집 공고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4341,7 +4357,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20260224</t>
+          <t>20260324</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4351,28 +4367,28 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019551&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>D-119</t>
+          <t>D-118</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>경북</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026 다자녀 전세임대 입주자 수시모집 공고</t>
+          <t>2026년 청년 전세임대 1순위 입주자 수시모집</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4382,7 +4398,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20260324</t>
+          <t>20260224</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4392,28 +4408,28 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019546&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
+          <t>https://apply.lh.or.kr/lhapply/apply/wt/wrtanc/selectWrtancInfo.do?panId=2015122300019376&amp;ccrCnntSysDsCd=03&amp;uppAisTpCd=13&amp;aisTpCd=17&amp;mi=1026</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I90" t="inlineStr">
         <